--- a/temp/espc-2/searchByMAC-9.xlsx
+++ b/temp/espc-2/searchByMAC-9.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="48">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,30 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -484,13 +508,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB211"/>
+  <dimension ref="A1:AD212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,17 +534,21 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -528,23 +556,17 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -552,81 +574,114 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>16</v>
+      </c>
+      <c r="W4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="W5">
+        <v>11</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="X6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>3</v>
@@ -640,15 +695,26 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="X7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
@@ -662,93 +728,163 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>11</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="W9">
+        <v>11</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="K10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>11</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W11">
+        <v>11</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>3</v>
@@ -762,15 +898,42 @@
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>3</v>
@@ -784,15 +947,42 @@
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
@@ -806,15 +996,42 @@
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>11</v>
+      </c>
+      <c r="O14" s="1">
+        <v>6</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W14">
+        <v>11</v>
+      </c>
+      <c r="X14" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>3</v>
@@ -828,15 +1045,42 @@
       <c r="K15" s="2"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>13</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15" s="1">
+        <v>13</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -850,15 +1094,46 @@
       <c r="K16" s="2"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
+        <v>14</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -868,161 +1143,400 @@
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W17">
+        <v>11</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="1"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19">
+        <v>11</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22">
         <v>1</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="K23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>18</v>
@@ -1036,15 +1550,36 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>18</v>
@@ -1058,15 +1593,31 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>18</v>
@@ -1080,63 +1631,72 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="1"/>
+      <c r="Z27" s="1"/>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="1"/>
+      <c r="Z28" s="1"/>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>18</v>
@@ -1150,15 +1710,12 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>18</v>
@@ -1172,15 +1729,12 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>18</v>
@@ -1194,15 +1748,22 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N31">
+        <v>16</v>
+      </c>
+      <c r="W31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1212,15 +1773,14 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1232,19 +1792,26 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="B34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1254,15 +1821,24 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>19</v>
@@ -1276,15 +1852,24 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>19</v>
@@ -1298,15 +1883,24 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>19</v>
@@ -1320,18 +1914,23 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1342,18 +1941,27 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1368,11 +1976,11 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>19</v>
@@ -1390,11 +1998,11 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>19</v>
@@ -1412,11 +2020,11 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>19</v>
@@ -1434,14 +2042,14 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -1456,14 +2064,14 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -1478,11 +2086,11 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>19</v>
@@ -1500,11 +2108,11 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>19</v>
@@ -1519,14 +2127,18 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -1537,14 +2149,12 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1559,19 +2169,14 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1585,14 +2190,14 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
@@ -1610,17 +2215,17 @@
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -1632,8 +2237,8 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
@@ -1642,10 +2247,10 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -1657,8 +2262,8 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
@@ -1667,10 +2272,10 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -1692,7 +2297,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>23</v>
@@ -1717,10 +2322,10 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -1742,7 +2347,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>21</v>
@@ -1767,7 +2372,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>21</v>
@@ -1792,7 +2397,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>21</v>
@@ -1817,10 +2422,10 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -1834,15 +2439,18 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -1861,7 +2469,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>21</v>
@@ -1882,8 +2490,12 @@
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="C62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -1899,9 +2511,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -1916,22 +2526,14 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="B64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -1955,10 +2557,10 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -1983,10 +2585,10 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -2011,10 +2613,10 @@
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -2039,7 +2641,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>25</v>
@@ -2067,10 +2669,10 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -2095,10 +2697,10 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -2113,8 +2715,8 @@
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="R70" s="1"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="2"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
@@ -2123,10 +2725,10 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -2141,8 +2743,8 @@
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
@@ -2151,7 +2753,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>24</v>
@@ -2179,7 +2781,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>24</v>
@@ -2200,17 +2802,17 @@
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="V73" s="1"/>
-      <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -2221,18 +2823,24 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
       <c r="P74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="V74" s="1"/>
+      <c r="W74" s="2"/>
+      <c r="X74" s="2"/>
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -2251,7 +2859,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>24</v>
@@ -2272,8 +2880,12 @@
     <row r="77" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
+      <c r="C77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -2289,9 +2901,7 @@
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -2303,28 +2913,17 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" s="1"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
-      <c r="V78" s="1"/>
-      <c r="W78" s="1"/>
-      <c r="X78" s="1"/>
-      <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
-      <c r="AB78" s="1"/>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="B79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -2341,8 +2940,8 @@
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
       <c r="V79" s="1"/>
-      <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
@@ -2351,10 +2950,10 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -2372,8 +2971,8 @@
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
       <c r="V80" s="1"/>
-      <c r="W80" s="1"/>
-      <c r="X80" s="1"/>
+      <c r="W80" s="2"/>
+      <c r="X80" s="2"/>
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
@@ -2382,10 +2981,10 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -2413,10 +3012,10 @@
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -2444,10 +3043,10 @@
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -2475,7 +3074,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>26</v>
@@ -2506,10 +3105,10 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -2530,17 +3129,17 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
       <c r="Z85" s="1"/>
-      <c r="AA85" s="2"/>
-      <c r="AB85" s="2"/>
+      <c r="AA85" s="1"/>
+      <c r="AB85" s="1"/>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -2557,15 +3156,21 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AA86" s="2"/>
+      <c r="AB86" s="2"/>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -2579,12 +3184,15 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>27</v>
@@ -2606,7 +3214,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>27</v>
@@ -2628,10 +3236,10 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -2650,10 +3258,10 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -2671,8 +3279,12 @@
     <row r="92" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+      <c r="C92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
@@ -2688,9 +3300,7 @@
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -2705,25 +3315,14 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
-      <c r="R93" s="1"/>
-      <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
-      <c r="V93" s="1"/>
-      <c r="W93" s="1"/>
-      <c r="X93" s="1"/>
-      <c r="Z93" s="1"/>
-      <c r="AA93" s="1"/>
-      <c r="AB93" s="1"/>
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -2750,10 +3349,10 @@
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -2781,10 +3380,10 @@
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -2812,10 +3411,10 @@
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -2843,10 +3442,10 @@
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -2874,7 +3473,7 @@
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>28</v>
@@ -2905,7 +3504,7 @@
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>28</v>
@@ -2936,10 +3535,10 @@
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -2967,7 +3566,7 @@
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>29</v>
@@ -2998,7 +3597,7 @@
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>29</v>
@@ -3029,10 +3628,10 @@
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -3053,14 +3652,14 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
       <c r="Z104" s="1"/>
-      <c r="AA104" s="2"/>
-      <c r="AB104" s="2"/>
+      <c r="AA104" s="1"/>
+      <c r="AB104" s="1"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>28</v>
@@ -3077,15 +3676,24 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Z105" s="1"/>
+      <c r="AA105" s="2"/>
+      <c r="AB105" s="2"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -3103,8 +3711,12 @@
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="C107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -3120,15 +3732,11 @@
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
-      <c r="B108" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
@@ -3139,27 +3747,18 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
-      <c r="R108" s="1"/>
-      <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
-      <c r="V108" s="1"/>
-      <c r="W108" s="1"/>
-      <c r="X108" s="1"/>
-      <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
+      <c r="F109" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
@@ -3184,7 +3783,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>5</v>
@@ -3215,23 +3814,19 @@
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
-      <c r="G111" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
-      <c r="K111" s="2"/>
-      <c r="L111" s="2"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
@@ -3250,19 +3845,23 @@
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="1"/>
+      <c r="G112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="1"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
@@ -3281,7 +3880,7 @@
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>5</v>
@@ -3312,7 +3911,7 @@
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>5</v>
@@ -3336,14 +3935,14 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Z114" s="1"/>
-      <c r="AA114" s="2"/>
-      <c r="AB114" s="2"/>
+      <c r="AA114" s="1"/>
+      <c r="AB114" s="1"/>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>5</v>
@@ -3367,26 +3966,22 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Z115" s="1"/>
-      <c r="AA115" s="1"/>
-      <c r="AB115" s="1"/>
+      <c r="AA115" s="2"/>
+      <c r="AB115" s="2"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
-      <c r="G116" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
@@ -3409,7 +4004,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>30</v>
@@ -3417,7 +4012,7 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>30</v>
@@ -3444,15 +4039,19 @@
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
+      <c r="G118" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
@@ -3475,10 +4074,10 @@
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -3506,7 +4105,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>5</v>
@@ -3523,15 +4122,24 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Z120" s="1"/>
+      <c r="AA120" s="1"/>
+      <c r="AB120" s="1"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
@@ -3549,8 +4157,12 @@
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="C122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
@@ -3566,9 +4178,7 @@
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
-      <c r="B123" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -3586,13 +4196,11 @@
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -3610,7 +4218,7 @@
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>33</v>
@@ -3632,7 +4240,7 @@
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>33</v>
@@ -3654,7 +4262,7 @@
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>33</v>
@@ -3676,7 +4284,7 @@
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>33</v>
@@ -3698,7 +4306,7 @@
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>33</v>
@@ -3720,7 +4328,7 @@
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>33</v>
@@ -3742,7 +4350,7 @@
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>33</v>
@@ -3764,7 +4372,7 @@
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>33</v>
@@ -3786,7 +4394,7 @@
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>33</v>
@@ -3808,7 +4416,7 @@
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>33</v>
@@ -3830,7 +4438,7 @@
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>33</v>
@@ -3852,7 +4460,7 @@
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>33</v>
@@ -3873,8 +4481,12 @@
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="C137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -3890,9 +4502,7 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
-      <c r="B138" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -3910,13 +4520,11 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="B139" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
@@ -3934,7 +4542,7 @@
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>34</v>
@@ -3956,7 +4564,7 @@
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>34</v>
@@ -3978,7 +4586,7 @@
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>34</v>
@@ -4000,7 +4608,7 @@
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>34</v>
@@ -4022,7 +4630,7 @@
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>34</v>
@@ -4044,7 +4652,7 @@
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>34</v>
@@ -4066,7 +4674,7 @@
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>34</v>
@@ -4088,7 +4696,7 @@
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>34</v>
@@ -4110,7 +4718,7 @@
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>34</v>
@@ -4132,7 +4740,7 @@
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>34</v>
@@ -4154,7 +4762,7 @@
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>34</v>
@@ -4176,7 +4784,7 @@
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>34</v>
@@ -4197,8 +4805,12 @@
     <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
+      <c r="C152" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
@@ -4214,15 +4826,11 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
-      <c r="B153" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="B153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="F153" s="1"/>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -4236,15 +4844,15 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="B154" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="1"/>
+      <c r="F154" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -4260,19 +4868,15 @@
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
-      <c r="G155" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
@@ -4286,15 +4890,19 @@
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
-      <c r="H156" s="1"/>
+      <c r="G156" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
@@ -4308,19 +4916,15 @@
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
@@ -4334,15 +4938,19 @@
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
-      <c r="H158" s="1"/>
+      <c r="G158" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
@@ -4356,7 +4964,7 @@
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>35</v>
@@ -4378,7 +4986,7 @@
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>35</v>
@@ -4400,7 +5008,7 @@
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>35</v>
@@ -4422,19 +5030,15 @@
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
-      <c r="G162" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
@@ -4448,15 +5052,19 @@
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
-      <c r="G163" s="1"/>
-      <c r="H163" s="1"/>
+      <c r="G163" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
@@ -4470,7 +5078,7 @@
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>35</v>
@@ -4492,7 +5100,7 @@
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>35</v>
@@ -4514,7 +5122,7 @@
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>35</v>
@@ -4535,8 +5143,12 @@
     <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="C167" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
@@ -4552,9 +5164,7 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
-      <c r="B168" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -4569,19 +5179,14 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
       <c r="P168" s="1"/>
-      <c r="R168" s="1"/>
-      <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="B169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
@@ -4602,7 +5207,7 @@
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>36</v>
@@ -4627,7 +5232,7 @@
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>36</v>
@@ -4652,7 +5257,7 @@
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>36</v>
@@ -4677,7 +5282,7 @@
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>36</v>
@@ -4702,7 +5307,7 @@
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>36</v>
@@ -4727,7 +5332,7 @@
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>36</v>
@@ -4752,7 +5357,7 @@
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>36</v>
@@ -4777,7 +5382,7 @@
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>36</v>
@@ -4802,7 +5407,7 @@
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>36</v>
@@ -4827,10 +5432,10 @@
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
@@ -4845,17 +5450,17 @@
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
       <c r="R179" s="1"/>
-      <c r="S179" s="2"/>
-      <c r="T179" s="2"/>
+      <c r="S179" s="1"/>
+      <c r="T179" s="1"/>
     </row>
     <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
@@ -4870,14 +5475,14 @@
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
       <c r="R180" s="1"/>
-      <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
+      <c r="S180" s="2"/>
+      <c r="T180" s="2"/>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>36</v>
@@ -4892,8 +5497,8 @@
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
       <c r="N181" s="1"/>
-      <c r="O181" s="2"/>
-      <c r="P181" s="2"/>
+      <c r="O181" s="1"/>
+      <c r="P181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -4901,8 +5506,12 @@
     <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="C182" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
@@ -4913,14 +5522,15 @@
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
       <c r="N182" s="1"/>
-      <c r="O182" s="1"/>
-      <c r="P182" s="1"/>
+      <c r="O182" s="2"/>
+      <c r="P182" s="2"/>
+      <c r="R182" s="1"/>
+      <c r="S182" s="1"/>
+      <c r="T182" s="1"/>
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
-      <c r="B183" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -4935,19 +5545,14 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
-      <c r="R183" s="1"/>
-      <c r="S183" s="1"/>
-      <c r="T183" s="1"/>
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="B184" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
@@ -4968,7 +5573,7 @@
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>38</v>
@@ -4993,7 +5598,7 @@
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>38</v>
@@ -5018,7 +5623,7 @@
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>38</v>
@@ -5043,7 +5648,7 @@
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>38</v>
@@ -5061,14 +5666,14 @@
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
       <c r="R188" s="1"/>
-      <c r="S188" s="2"/>
-      <c r="T188" s="2"/>
+      <c r="S188" s="1"/>
+      <c r="T188" s="1"/>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>38</v>
@@ -5086,14 +5691,14 @@
       <c r="O189" s="1"/>
       <c r="P189" s="1"/>
       <c r="R189" s="1"/>
-      <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="S189" s="2"/>
+      <c r="T189" s="2"/>
     </row>
     <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>38</v>
@@ -5118,7 +5723,7 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>38</v>
@@ -5143,7 +5748,7 @@
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>38</v>
@@ -5168,7 +5773,7 @@
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>38</v>
@@ -5193,7 +5798,7 @@
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>38</v>
@@ -5218,7 +5823,7 @@
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>38</v>
@@ -5243,7 +5848,7 @@
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>38</v>
@@ -5260,12 +5865,19 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
       <c r="P196" s="1"/>
+      <c r="R196" s="1"/>
+      <c r="S196" s="1"/>
+      <c r="T196" s="1"/>
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="C197" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
@@ -5281,9 +5893,7 @@
     </row>
     <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
-      <c r="B198" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -5301,13 +5911,11 @@
     </row>
     <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
-      <c r="B199" s="1"/>
-      <c r="C199" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="B199" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
@@ -5325,7 +5933,7 @@
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>39</v>
@@ -5347,7 +5955,7 @@
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>39</v>
@@ -5369,7 +5977,7 @@
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>39</v>
@@ -5391,7 +5999,7 @@
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>39</v>
@@ -5413,7 +6021,7 @@
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>39</v>
@@ -5435,7 +6043,7 @@
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>39</v>
@@ -5450,14 +6058,14 @@
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
       <c r="N205" s="1"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
+      <c r="O205" s="1"/>
+      <c r="P205" s="1"/>
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>39</v>
@@ -5472,14 +6080,14 @@
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
-      <c r="O206" s="1"/>
-      <c r="P206" s="1"/>
+      <c r="O206" s="2"/>
+      <c r="P206" s="2"/>
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>39</v>
@@ -5501,7 +6109,7 @@
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>39</v>
@@ -5523,7 +6131,7 @@
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>39</v>
@@ -5545,7 +6153,7 @@
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>39</v>
@@ -5567,7 +6175,7 @@
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>39</v>
@@ -5585,6 +6193,28 @@
       <c r="O211" s="1"/>
       <c r="P211" s="1"/>
     </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+      <c r="L212" s="1"/>
+      <c r="M212" s="1"/>
+      <c r="N212" s="1"/>
+      <c r="O212" s="1"/>
+      <c r="P212" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
